--- a/data/seed/portfolio/L-2025-9040/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-9040/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J187"/>
+  <dimension ref="A1:J141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -540,23 +540,23 @@
       <c r="B8" t="n">
         <v>100</v>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>3311000</v>
-      </c>
-      <c r="D8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n">
+        <v>11073000</v>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Samarqand Qurilish Materiallari MChJ</t>
+          <t>Gulshan Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>311741835</t>
+          <t>361481815</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000721195978001</t>
+          <t>20208000576522897001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №169/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6174</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>117189000</v>
+        <v>131573000</v>
       </c>
     </row>
     <row r="9">
@@ -580,37 +580,37 @@
       <c r="B9" t="n">
         <v>101</v>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>11592000</v>
-      </c>
-      <c r="D9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n">
+        <v>3486000</v>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Samarqand Qurilish Materiallari MChJ</t>
+          <t>Yulduz Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>311741835</t>
+          <t>398152432</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000721195978001</t>
+          <t>20208000764681463001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9291</t>
+          <t>Mahsulot uchun to'lov, shartn. №143/26, QQS 12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>105597000</v>
+        <v>135059000</v>
       </c>
     </row>
     <row r="10">
@@ -620,37 +620,37 @@
       <c r="B10" t="n">
         <v>102</v>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n">
-        <v>1361000</v>
-      </c>
+      <c r="C10" s="2" t="n">
+        <v>1895000</v>
+      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Termiz Trans Servis MChJ</t>
+          <t>Afrosiyob Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>215614818</t>
+          <t>396615468</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000515765228001</t>
+          <t>20208000992552358001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №563</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №94/26</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>106958000</v>
+        <v>133164000</v>
       </c>
     </row>
     <row r="11">
@@ -661,76 +661,76 @@
         <v>103</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>3535000</v>
+        <v>3045000</v>
       </c>
       <c r="D11" s="2" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qarshi Mehmonxona MChJ</t>
+          <t>Afrosiyob Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>252244188</t>
+          <t>396615468</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000444491128001</t>
+          <t>20208000992552358001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №30/26</t>
+          <t>Оплата за сырье по договору №81/26 от 03.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>103423000</v>
+        <v>130119000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n">
-        <v>4749000</v>
-      </c>
+      <c r="C12" s="2" t="n">
+        <v>101387000</v>
+      </c>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jizzax Poligraf MChJ</t>
+          <t>Bog'ishamol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>248391487</t>
+          <t>292921206</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000989998587001</t>
+          <t>20208000867142616001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3528</t>
+          <t>Предоплата за материалы по договору №39/26</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>108172000</v>
+        <v>28732000</v>
       </c>
     </row>
     <row r="13">
@@ -742,35 +742,35 @@
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>3614000</v>
+        <v>78793000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Termiz Trans Servis MChJ</t>
+          <t>Durdona Mebel MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>215614818</t>
+          <t>339148709</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000515765228001</t>
+          <t>20208000999858706001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №407 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №87/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>111786000</v>
+        <v>107525000</v>
       </c>
     </row>
     <row r="14">
@@ -780,37 +780,37 @@
       <c r="B14" t="n">
         <v>106</v>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>4517000</v>
-      </c>
-      <c r="D14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n">
+        <v>4826000</v>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Navro'z Qurilish Materiallari MChJ</t>
+          <t>Yulduz Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>240187768</t>
+          <t>398152432</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000945086482001</t>
+          <t>20208000764681463001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9416</t>
+          <t>Предоплата за товар по договору №124/26 от 06.07.2026</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>107269000</v>
+        <v>112351000</v>
       </c>
     </row>
     <row r="15">
@@ -820,58 +820,63 @@
       <c r="B15" t="n">
         <v>107</v>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>12768000</v>
-      </c>
-      <c r="D15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n">
+        <v>4168000</v>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Durdona Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>339148709</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000999858706001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>IYUN OYI UCHUN ISH HAQI, REESTR №7598</t>
+          <t>Предоплата за товар по договору №189/26 от 06.07.2026</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>94501000</v>
+        <v>116519000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B16" t="n">
         <v>108</v>
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>39219000</v>
+        <v>3410000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -881,77 +886,77 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №35/26 от 07.07.2026</t>
+          <t>Оплата по с/ф №1918 за поставленный товар</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>133720000</v>
+        <v>119929000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B17" t="n">
         <v>109</v>
       </c>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n">
-        <v>3476000</v>
+        <v>2526000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Toshkent Plastik XK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>259824283</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000748136880001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9984 07.07.2026, QQS bilan</t>
+          <t>ОПЛАТА ПО С/Ф №6843 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>137196000</v>
+        <v>122455000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1990000</v>
+        <v>1579000</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shodlik Qurilish AJ</t>
+          <t>Xiva Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>318892467</t>
+          <t>246828606</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000936687065001</t>
+          <t>20208000719285477001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -961,117 +966,112 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Ijara haqi iyul oyi uchun, shartnoma №81/24</t>
+          <t>Предоплата за материалы по договору №280/26</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>135206000</v>
+        <v>120876000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46212</v>
+        <v>46209</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n">
-        <v>14956000</v>
-      </c>
+      <c r="C19" s="2" t="n">
+        <v>4675000</v>
+      </c>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Afrosiyob Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>396615468</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000992552358001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Shartnoma №12/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товары согласно счет-фактуре №2907</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>150162000</v>
+        <v>116201000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46212</v>
+        <v>46209</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n">
-        <v>2644000</v>
-      </c>
+      <c r="C20" s="2" t="n">
+        <v>12768000</v>
+      </c>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>356268930</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SHARTNOMA №198/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>152806000</v>
+        <v>103433000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46212</v>
+        <v>46210</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n">
-        <v>2570000</v>
+        <v>21420000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1081,37 +1081,37 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3883</t>
+          <t>Предоплата за товар по договору №94/26 от 07.07.2026</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>155376000</v>
+        <v>124853000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46212</v>
+        <v>46210</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n">
-        <v>1470000</v>
+        <v>2068000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Gulshan Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>361481815</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000576522897001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1121,37 +1121,37 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7770</t>
+          <t>Предоплата за товар по дог. №58/26 от 07.07.2026</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>156846000</v>
+        <v>126921000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>3249000</v>
-      </c>
-      <c r="D23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n">
+        <v>5526000</v>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Samarqand Qurilish Materiallari MChJ</t>
+          <t>Gulshan Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>311741835</t>
+          <t>361481815</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000721195978001</t>
+          <t>20208000576522897001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1161,72 +1161,77 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №560</t>
+          <t>Оплата по счет-фактуре №943 за поставленный товар</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>153597000</v>
+        <v>132447000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46213</v>
+        <v>46211</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>29800000</v>
-      </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>4405000</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-9040)</t>
+          <t>Kamalak Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>16307000243693009417</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-9040 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата за товар по счет-фактуре №7725 от 08.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>123797000</v>
+        <v>136852000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46216</v>
+        <v>46212</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n">
-        <v>16347000</v>
+        <v>4303000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Gulshan Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>361481815</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000576522897001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1236,77 +1241,77 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6473 13.07.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №976 за поставленный товар</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>140144000</v>
+        <v>141155000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46216</v>
+        <v>46212</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n">
-        <v>13767000</v>
-      </c>
+      <c r="C26" s="2" t="n">
+        <v>1990000</v>
+      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Navro'z Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>313530644</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000179955104001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Shartnoma №65/26 bo'yicha oldindan to'lov</t>
+          <t>Арендная плата за июль 2026г. по дог. №15/25</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>153911000</v>
+        <v>139165000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>2415000</v>
+        <v>4897000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1316,37 +1321,37 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6890 за поставленный товар</t>
+          <t>Предоплата за товар по договору №227/26 от 10.07.2026</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>156326000</v>
+        <v>144062000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n">
-        <v>2289000</v>
-      </c>
+      <c r="C28" s="2" t="n">
+        <v>2790000</v>
+      </c>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Qarshi Plastik AJ</t>
+          <t>Xiva Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>265213054</t>
+          <t>246828606</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000371474384001</t>
+          <t>20208000719285477001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1356,91 +1361,86 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №199/26, QQS 12%</t>
+          <t>Предоплата за материалы по договору №180/26</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>158615000</v>
+        <v>141272000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n">
-        <v>1550000</v>
-      </c>
+      <c r="C29" s="2" t="n">
+        <v>29800000</v>
+      </c>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Termiz Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>215614818</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-9040)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000515765228001</t>
+          <t>16307000243693009417</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6009 13.07.2026, QQS bilan</t>
+          <t>Kredit shartnomasi L-2025-9040 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>160165000</v>
+        <v>111472000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>8488000</v>
+        <v>53315000</v>
       </c>
       <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Samarqand Qurilish Materiallari MChJ</t>
+          <t>Xiva Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>311741835</t>
+          <t>246828606</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000721195978001</t>
+          <t>20208000719285477001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №98/26 от 13.07.2026, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №7/26</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>151677000</v>
+        <v>58157000</v>
       </c>
     </row>
     <row r="31">
@@ -1450,23 +1450,23 @@
       <c r="B31" t="n">
         <v>123</v>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>11435000</v>
-      </c>
-      <c r="D31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n">
+        <v>4538000</v>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Samarqand Qurilish Materiallari MChJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>311741835</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000721195978001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1476,37 +1476,37 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №69/26</t>
+          <t>Оплата за продукцию по договору №19/26, НДС 12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>140242000</v>
+        <v>62695000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n">
-        <v>3116000</v>
+        <v>3918000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Termiz Trans Servis MChJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>215614818</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000515765228001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1516,51 +1516,51 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №280/26 от 14.07.2026</t>
+          <t>Оплата по счет-фактуре №750 за поставленный товар</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>143358000</v>
+        <v>66613000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n">
-        <v>1571000</v>
-      </c>
+      <c r="C33" s="2" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Bog'ishamol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>292921206</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000867142616001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №227</t>
+          <t>Оплата за сырье по договору №210/26 от 13.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>144929000</v>
+        <v>65313000</v>
       </c>
     </row>
     <row r="34">
@@ -1570,37 +1570,37 @@
       <c r="B34" t="n">
         <v>126</v>
       </c>
-      <c r="C34" s="2" t="n">
-        <v>1741000</v>
-      </c>
-      <c r="D34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n">
+        <v>3074000</v>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ijtimoiy soliq</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №273/26 ОТ 14.07.2026</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>143188000</v>
+        <v>68387000</v>
       </c>
     </row>
     <row r="35">
@@ -1610,77 +1610,77 @@
       <c r="B35" t="n">
         <v>127</v>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>1741000</v>
-      </c>
-      <c r="D35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n">
+        <v>2060000</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>JShDS iyun oyi uchun</t>
+          <t>Предоплата за товар по договору №32/26 от 14.07.2026</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>141447000</v>
+        <v>70447000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n">
-        <v>13160000</v>
-      </c>
+      <c r="C36" s="2" t="n">
+        <v>2007000</v>
+      </c>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Xiva Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>246828606</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000719285477001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №9335 15.07.2026, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактуре №5400</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>154607000</v>
+        <v>68440000</v>
       </c>
     </row>
     <row r="37">
@@ -1690,37 +1690,37 @@
       <c r="B37" t="n">
         <v>129</v>
       </c>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n">
-        <v>6557000</v>
-      </c>
+      <c r="C37" s="2" t="n">
+        <v>1741000</v>
+      </c>
+      <c r="D37" s="2" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2957</t>
+          <t>Уплата социального налога за июнь</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>161164000</v>
+        <v>66699000</v>
       </c>
     </row>
     <row r="38">
@@ -1731,76 +1731,76 @@
         <v>130</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>4513000</v>
+        <v>1741000</v>
       </c>
       <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saodat Un Mahsulotlari XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>212729239</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000763758455001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9170</t>
+          <t>НДФЛза июнь 2026</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>156651000</v>
+        <v>64958000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n">
-        <v>2019000</v>
-      </c>
+      <c r="C39" s="2" t="n">
+        <v>5734000</v>
+      </c>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Tong Qog'oz XK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>203271276</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000844133481001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1302 16.07.2026, QQS bilan</t>
+          <t>Оплата за сырье по договору №136/26 от 15.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>158670000</v>
+        <v>59224000</v>
       </c>
     </row>
     <row r="40">
@@ -1812,75 +1812,75 @@
       </c>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n">
-        <v>1507000</v>
+        <v>4800000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Toshkent Plastik XK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>259824283</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000748136880001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №256/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №2717 за поставленный товар</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>160177000</v>
+        <v>64024000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46220</v>
+        <v>46219</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>6652000</v>
+        <v>1619000</v>
       </c>
       <c r="D41" s="2" t="n"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Qarshi Mehmonxona MChJ</t>
+          <t>Ziyo Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>252244188</t>
+          <t>314566779</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000444491128001</t>
+          <t>20208000308579769001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №82/26</t>
+          <t>Оплата за товары согласно счет-фактуре №2005</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>153525000</v>
+        <v>62405000</v>
       </c>
     </row>
     <row r="42">
@@ -1890,23 +1890,23 @@
       <c r="B42" t="n">
         <v>134</v>
       </c>
-      <c r="C42" s="2" t="n">
-        <v>7685000</v>
-      </c>
-      <c r="D42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n">
+        <v>9276000</v>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Qog'oz MChJ</t>
+          <t>Durdona Mebel MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>397204262</t>
+          <t>339148709</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000211896951001</t>
+          <t>20208000999858706001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1916,37 +1916,37 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №241/26, QQS bilan</t>
+          <t>Оплата за продукцию по договору №68/26, НДС 12%</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>145840000</v>
+        <v>71681000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46223</v>
+        <v>46220</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>9470000</v>
+        <v>1861000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1956,11 +1956,11 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3311</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №4809 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>155310000</v>
+        <v>73542000</v>
       </c>
     </row>
     <row r="44">
@@ -1970,23 +1970,23 @@
       <c r="B44" t="n">
         <v>136</v>
       </c>
-      <c r="C44" s="2" t="n">
-        <v>13443000</v>
-      </c>
-      <c r="D44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n">
+        <v>32883000</v>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Samarqand Qurilish Materiallari MChJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>311741835</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000721195978001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №168/26, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №4184 от 20.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>141867000</v>
+        <v>106425000</v>
       </c>
     </row>
     <row r="45">
@@ -2011,262 +2011,262 @@
         <v>137</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>59539000</v>
+        <v>3237000</v>
       </c>
       <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Qarshi Mehmonxona MChJ</t>
+          <t>Xiva Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>252244188</t>
+          <t>246828606</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000444491128001</t>
+          <t>20208000719285477001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №110/26 от 20.07.2026, НДС 12%</t>
+          <t>Предоплата за материалы по договору №69/26</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>82328000</v>
+        <v>103188000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n">
-        <v>5913000</v>
-      </c>
+      <c r="C46" s="2" t="n">
+        <v>5054000</v>
+      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Xiva Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>246828606</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000719285477001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Shartnoma №73/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за сырье по договору №94/26 от 20.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>88241000</v>
+        <v>98134000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n">
-        <v>2045000</v>
-      </c>
+      <c r="C47" s="2" t="n">
+        <v>5527000</v>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Xiva Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>246828606</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000719285477001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnom №212/26, QQS 12%</t>
+          <t>Оплата за транспортные услуги по договору №153/26</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>90286000</v>
+        <v>92607000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>10360000</v>
-      </c>
-      <c r="D48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n">
+        <v>4910000</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Navro'z Qurilish Materiallari MChJ</t>
+          <t>Gulshan Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>240187768</t>
+          <t>361481815</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000945086482001</t>
+          <t>20208000576522897001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №1711</t>
+          <t>Оплата по счет-фактуре №5397 за поставленный товар</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>79926000</v>
+        <v>97517000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n">
-        <v>8078000</v>
+        <v>2015000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Termiz Trans Servis MChJ</t>
+          <t>Durdona Mebel MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>215614818</t>
+          <t>339148709</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000515765228001</t>
+          <t>20208000999858706001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №195/26 ОТ 22.07.2026</t>
+          <t>Оплата по счет-фактуре №9203 за поставленный товар</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>88004000</v>
+        <v>99532000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n">
-        <v>3023000</v>
-      </c>
+      <c r="C50" s="2" t="n">
+        <v>3310000</v>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Jizzax Poligraf MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>248391487</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000989998587001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №100/26, QQS 12%</t>
+          <t>Уплата налога на добавленную стоимость за июнь</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>91027000</v>
+        <v>96222000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46225</v>
+        <v>46230</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>3381000</v>
-      </c>
-      <c r="D51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n">
+        <v>19416000</v>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Samarqand Qurilish Materiallari MChJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>311741835</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000721195978001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2276,117 +2276,117 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №153/26</t>
+          <t>Оплата по счет-фактуре №2016 за поставленный товар</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>87646000</v>
+        <v>115638000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>1244000</v>
-      </c>
-      <c r="D52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n">
+        <v>6195000</v>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000204982757001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov iyul</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №271/26 ОТ 27.07.2026</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>86402000</v>
+        <v>121833000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
-      <c r="C53" s="2" t="n">
-        <v>3177000</v>
-      </c>
-      <c r="D53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n">
+        <v>3155000</v>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Yulduz Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>398152432</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000764681463001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №266/26, НДС 12%</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>83225000</v>
+        <v>124988000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n">
-        <v>12127000</v>
+        <v>2671000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Gulshan Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>361481815</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000576522897001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2396,51 +2396,51 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Shartnoma №152/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №34/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>95352000</v>
+        <v>127659000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n">
-        <v>2378000</v>
-      </c>
+      <c r="C55" s="2" t="n">
+        <v>1244000</v>
+      </c>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Termiz Trans Servis MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>215614818</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000515765228001</t>
+          <t>20208000083652130001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9862 24.07.2026, QQS bilan</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>97730000</v>
+        <v>126415000</v>
       </c>
     </row>
     <row r="56">
@@ -2450,37 +2450,37 @@
       <c r="B56" t="n">
         <v>148</v>
       </c>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n">
-        <v>38176000</v>
-      </c>
+      <c r="C56" s="2" t="n">
+        <v>1310000</v>
+      </c>
+      <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Afrosiyob Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>396615468</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000992552358001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4347 за поставленный товар</t>
+          <t>Оплата за сырье по дог. №130/26 от 27.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>135906000</v>
+        <v>125105000</v>
       </c>
     </row>
     <row r="57">
@@ -2490,37 +2490,37 @@
       <c r="B57" t="n">
         <v>149</v>
       </c>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n">
-        <v>11037000</v>
-      </c>
+      <c r="C57" s="2" t="n">
+        <v>10919000</v>
+      </c>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Jizzax Poligraf MChJ</t>
+          <t>Afrosiyob Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>248391487</t>
+          <t>396615468</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000989998587001</t>
+          <t>20208000992552358001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №3137 за поставленный товар</t>
+          <t>Оплата за товары согласно счет-фактуре №7956</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>146943000</v>
+        <v>114186000</v>
       </c>
     </row>
     <row r="58">
@@ -2530,303 +2530,298 @@
       <c r="B58" t="n">
         <v>150</v>
       </c>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n">
-        <v>9541000</v>
-      </c>
+      <c r="C58" s="2" t="n">
+        <v>15079000</v>
+      </c>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Xiva Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>246828606</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000719285477001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №81/26, QQS 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №8480</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>156484000</v>
+        <v>99107000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n">
-        <v>5062000</v>
+        <v>14865000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Toshkent Plastik XK</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>259824283</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000748136880001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4541 27.07.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №3789 за поставленный товар</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>161546000</v>
+        <v>113972000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>2272000</v>
+        <v>5536000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Yulduz Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>398152432</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000764681463001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №246/26, QQS 12%</t>
+          <t>Оплата по с/ф №2499 за поставленный товар</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>163818000</v>
+        <v>119508000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
-      <c r="C61" s="2" t="n">
-        <v>10015000</v>
-      </c>
-      <c r="D61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n">
+        <v>3753000</v>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Qarshi Mehmonxona MChJ</t>
+          <t>Gulshan Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>252244188</t>
+          <t>361481815</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000444491128001</t>
+          <t>20208000576522897001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №121/26</t>
+          <t>Оплата по счет-фактуре №3727 за поставленный товар</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>153803000</v>
+        <v>123261000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>27427000</v>
+        <v>1309000</v>
       </c>
       <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Qog'oz MChJ</t>
+          <t>Ziyo Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>397204262</t>
+          <t>314566779</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000211896951001</t>
+          <t>20208000308579769001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №199/26</t>
+          <t>Оплата за транспортные услуги по договору №291/26</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>126376000</v>
+        <v>121952000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="n">
-        <v>4372000</v>
-      </c>
+      <c r="C63" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>356268930</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Shartnoma №79/26 bo'yicha oldindan to'lov</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>130748000</v>
+        <v>121652000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
-      <c r="C64" s="2" t="n"/>
-      <c r="D64" s="2" t="n">
-        <v>3990000</v>
-      </c>
+      <c r="C64" s="2" t="n">
+        <v>2086000</v>
+      </c>
+      <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Afrosiyob Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>396615468</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000992552358001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Shartnoma №279/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за транспортные услуги по договору №295/26</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>134738000</v>
+        <v>119566000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n">
-        <v>1486000</v>
+        <v>22424000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2836,117 +2831,117 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7026 30.07.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №1695 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>136224000</v>
+        <v>141990000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n">
-        <v>1366000</v>
+        <v>11466000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Toshkent Plastik XK</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>259824283</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000748136880001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Shartnoma №37/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №2184 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>137590000</v>
+        <v>153456000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n">
-        <v>4221000</v>
-      </c>
+      <c r="C67" s="2" t="n">
+        <v>31479000</v>
+      </c>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sarbon Metall Servis MChJ</t>
+          <t>Bog'ishamol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>336981524</t>
+          <t>292921206</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000287646814001</t>
+          <t>20208000867142616001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №37/26, QQS 12%</t>
+          <t>Оплата за транспортные услуги по дог. №19/26</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>141811000</v>
+        <v>121977000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>1877000</v>
+        <v>26495000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -2956,232 +2951,232 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Shartnoma №109/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по с/ф №6019 за поставленный товар</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>143688000</v>
+        <v>148472000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46234</v>
+        <v>46239</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
-      <c r="C69" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n">
+        <v>13399000</v>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Gulshan Tur Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>361481815</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000576522897001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Оплата по счет-фактуре №2217 за поставленный товар</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>143388000</v>
+        <v>161871000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46234</v>
+        <v>46239</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>6140000</v>
+        <v>13535000</v>
       </c>
       <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Navro'z Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>240187768</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000945086482001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №42/26, QQS bilan</t>
+          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>137248000</v>
+        <v>148336000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46234</v>
+        <v>46239</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>24073000</v>
+        <v>16378000</v>
       </c>
       <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Saodat Un Mahsulotlari XK</t>
+          <t>Afrosiyob Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>212729239</t>
+          <t>396615468</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000763758455001</t>
+          <t>20208000992552358001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №195/26</t>
+          <t>Предоплата за материалы по договору №125/26</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>113175000</v>
+        <v>131958000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
       <c r="C72" s="2" t="n"/>
       <c r="D72" s="2" t="n">
-        <v>9893000</v>
+        <v>40575000</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Toshkent Plastik XK</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>259824283</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000748136880001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №210/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7055 06.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>123068000</v>
+        <v>172533000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n">
-        <v>8583000</v>
-      </c>
+      <c r="C73" s="2" t="n">
+        <v>14530000</v>
+      </c>
+      <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Termiz Trans Servis MChJ</t>
+          <t>Bog'ishamol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>215614818</t>
+          <t>292921206</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000515765228001</t>
+          <t>20208000867142616001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №263/26 ОТ 03.08.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №174</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>131651000</v>
+        <v>158003000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n">
-        <v>5988000</v>
+        <v>14773000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3191,237 +3186,232 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7497</t>
+          <t>Оплата за продукцию по договору №244/26, НДС 12%</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>137639000</v>
+        <v>172776000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
       <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="n">
-        <v>5957000</v>
+        <v>8357000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Qarshi Mebel MChJ</t>
+          <t>Gulshan Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>229145667</t>
+          <t>361481815</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000933085797001</t>
+          <t>20208000576522897001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4346</t>
+          <t>Предоплата за товар по договору №288/26 от 10.08.2026</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>143596000</v>
+        <v>181133000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n">
-        <v>3013000</v>
-      </c>
+      <c r="C76" s="2" t="n">
+        <v>2110000</v>
+      </c>
+      <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Namangan Mato MChJ</t>
+          <t>Navro'z Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>271598242</t>
+          <t>313530644</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000367481368001</t>
+          <t>20208000179955104001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №909 03.08.2026, QQS bilan</t>
+          <t>Арендная плата за август 2026 г. по дог. №15/25</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>146609000</v>
+        <v>179023000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n">
-        <v>2783000</v>
-      </c>
+      <c r="C77" s="2" t="n">
+        <v>15432000</v>
+      </c>
+      <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Qarshi Plastik AJ</t>
+          <t>Afrosiyob Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>265213054</t>
+          <t>396615468</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000371474384001</t>
+          <t>20208000992552358001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4722</t>
+          <t>Оплата за товары согласно счет-фактуре №3518</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>149392000</v>
+        <v>163591000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
-      <c r="C78" s="2" t="n"/>
-      <c r="D78" s="2" t="n">
-        <v>2419000</v>
-      </c>
+      <c r="C78" s="2" t="n">
+        <v>29800000</v>
+      </c>
+      <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>356268930</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-9040)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>16307000243693009417</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №74/26, QQS 12%</t>
+          <t>Kredit shartnomasi L-2025-9040 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>151811000</v>
+        <v>133791000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>17701000</v>
+        <v>54495000</v>
       </c>
       <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Samarqand Qurilish Materiallari MChJ</t>
+          <t>Xiva Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>311741835</t>
+          <t>246828606</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000721195978001</t>
+          <t>20208000719285477001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №275/26</t>
+          <t>Предоплата за материалы по договору №39/26</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>134110000</v>
+        <v>79296000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46238</v>
+        <v>46246</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
       <c r="C80" s="2" t="n"/>
       <c r="D80" s="2" t="n">
-        <v>2757000</v>
+        <v>10303000</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Termiz Trans Servis MChJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>215614818</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000515765228001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3431,77 +3421,77 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №121/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №158/26 от 12.08.2026</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>136867000</v>
+        <v>89599000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46238</v>
+        <v>46246</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n">
-        <v>2279000</v>
+        <v>9611000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Qarshi Plastik AJ</t>
+          <t>Durdona Mebel MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>265213054</t>
+          <t>339148709</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000371474384001</t>
+          <t>20208000999858706001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №257/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №8007 за поставленный товар</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>139146000</v>
+        <v>99210000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46239</v>
+        <v>46248</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
       <c r="C82" s="2" t="n"/>
       <c r="D82" s="2" t="n">
-        <v>4855000</v>
+        <v>58164000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3511,37 +3501,37 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №3079 05.08.2026, QQS bilan</t>
+          <t>Shartnoma №224/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>144001000</v>
+        <v>157374000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46239</v>
+        <v>46248</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
-      <c r="C83" s="2" t="n">
-        <v>5154000</v>
-      </c>
-      <c r="D83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n">
+        <v>21731000</v>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Samarqand Qurilish Materiallari MChJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>311741835</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000721195978001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3551,77 +3541,77 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9429</t>
+          <t>Предоплата за товар по договору №141/26 от 14.08.2026</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>138847000</v>
+        <v>179105000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46239</v>
+        <v>46251</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
-      <c r="C84" s="2" t="n">
-        <v>11641000</v>
-      </c>
-      <c r="D84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n">
+        <v>10908000</v>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Qog'oz MChJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>397204262</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000211896951001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №240/26, QQS bilan</t>
+          <t>Оплата по с/ф №6643 за поставленный товар</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>127206000</v>
+        <v>190013000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46240</v>
+        <v>46251</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
       <c r="C85" s="2" t="n"/>
       <c r="D85" s="2" t="n">
-        <v>11096000</v>
+        <v>6795000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Gulshan Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>361481815</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000576522897001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3631,112 +3621,117 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Shartnoma №61/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №221/26 от 17.08.2026</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>138302000</v>
+        <v>196808000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46240</v>
+        <v>46251</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
       <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="n">
-        <v>3561000</v>
+        <v>6066000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Qarshi Plastik AJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>265213054</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000371474384001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Shartnoma №202/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7209 17.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>141863000</v>
+        <v>202874000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46240</v>
+        <v>46251</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
-      <c r="C87" s="2" t="n">
-        <v>13535000</v>
-      </c>
-      <c r="D87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n">
+        <v>5844000</v>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Kamalak Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ish haqi, reestr №2629</t>
+          <t>Оплата по счет-фактуре №1206 за поставленный товар</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>128328000</v>
+        <v>208718000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
       <c r="C88" s="2" t="n"/>
       <c r="D88" s="2" t="n">
-        <v>21441000</v>
+        <v>5515000</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Termiz Trans Servis MChJ</t>
+          <t>Gulshan Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>215614818</t>
+          <t>361481815</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000515765228001</t>
+          <t>20208000576522897001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3746,157 +3741,157 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>SHARTNOMA №232/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за продукцию по дог. №57/26, НДС 12%</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>149769000</v>
+        <v>214233000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
-      <c r="C89" s="2" t="n"/>
-      <c r="D89" s="2" t="n">
-        <v>13193000</v>
-      </c>
+      <c r="C89" s="2" t="n">
+        <v>1846000</v>
+      </c>
+      <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4876 10.08.2026, QQS bilan</t>
+          <t>Уплата социального налога за июль</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>162962000</v>
+        <v>212387000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
-      <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n">
-        <v>10386000</v>
-      </c>
+      <c r="C90" s="2" t="n">
+        <v>1846000</v>
+      </c>
+      <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3012</t>
+          <t>Налог на доходы физических лиц за июль 2026 г.</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>173348000</v>
+        <v>210541000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n">
-        <v>4084000</v>
-      </c>
+      <c r="C91" s="2" t="n">
+        <v>12921000</v>
+      </c>
+      <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Afrosiyob Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>396615468</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000992552358001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №9104 за поставленный товар</t>
+          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №279/26</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>177432000</v>
+        <v>197620000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>2110000</v>
+        <v>40326000</v>
       </c>
       <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Shodlik Qurilish AJ</t>
+          <t>Xiva Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>318892467</t>
+          <t>246828606</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000936687065001</t>
+          <t>20208000719285477001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3906,272 +3901,272 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Аренда помещения за август, дог. №81/24</t>
+          <t>Предоплата за материалы по дог. №145/26</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>175322000</v>
+        <v>157294000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
-      <c r="C93" s="2" t="n">
-        <v>29800000</v>
-      </c>
-      <c r="D93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n">
+        <v>7632000</v>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-9040)</t>
+          <t>Kamalak Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>16307000243693009417</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-9040 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата по счет-фактуре №9954 за поставленный товар</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>145522000</v>
+        <v>164926000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
-      <c r="C94" s="2" t="n">
-        <v>53378000</v>
-      </c>
-      <c r="D94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n">
+        <v>11307000</v>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Saodat Un Mahsulotlari XK</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>212729239</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000763758455001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №2662</t>
+          <t>Оплата за продукцию по договору №73/26, НДС 12%</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>92144000</v>
+        <v>176233000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46248</v>
+        <v>46258</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>5134000</v>
+        <v>3496000</v>
       </c>
       <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Qarshi Mehmonxona MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>252244188</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000444491128001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №45/26</t>
+          <t>Уплата налога на добавленную стоимость за июль</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>87010000</v>
+        <v>172737000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46251</v>
+        <v>46260</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n">
-        <v>19503000</v>
-      </c>
+      <c r="C96" s="2" t="n">
+        <v>19300000</v>
+      </c>
+      <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Afrosiyob Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>396615468</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000992552358001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5478 за поставленный товар</t>
+          <t>Оплата за транспортные услуги по договору №10/26</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>106513000</v>
+        <v>153437000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46251</v>
+        <v>46260</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
-      <c r="C97" s="2" t="n"/>
-      <c r="D97" s="2" t="n">
-        <v>8049000</v>
-      </c>
+      <c r="C97" s="2" t="n">
+        <v>27705000</v>
+      </c>
+      <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Ilhom Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>277606955</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000466239816001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №154/26, QQS 12%</t>
+          <t>Предоплата за материалы по договору №243/26</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>114562000</v>
+        <v>125732000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46251</v>
+        <v>46261</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
-      <c r="C98" s="2" t="n"/>
-      <c r="D98" s="2" t="n">
-        <v>4891000</v>
-      </c>
+      <c r="C98" s="2" t="n">
+        <v>1319000</v>
+      </c>
+      <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000083652130001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8093 17.08.2026, QQS bilan</t>
+          <t>Оплата за электроэнергию за август 2026 г.</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>119453000</v>
+        <v>124413000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46251</v>
+        <v>46265</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
-      <c r="C99" s="2" t="n"/>
-      <c r="D99" s="2" t="n">
-        <v>4650000</v>
-      </c>
+      <c r="C99" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Qarshi Plastik AJ</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>265213054</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000371474384001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4181,37 +4176,37 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'ov h/f №4492</t>
+          <t>Комиссия банка а расчетно-кассовое обслуживание за август</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>124103000</v>
+        <v>124113000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46251</v>
+        <v>46266</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
       <c r="C100" s="2" t="n"/>
       <c r="D100" s="2" t="n">
-        <v>2851000</v>
+        <v>23244000</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Chirchiq Agro Servis AJ</t>
+          <t>Gulshan Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>320468286</t>
+          <t>361481815</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000657192854001</t>
+          <t>20208000576522897001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4221,197 +4216,197 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №269/26, QQS 12%</t>
+          <t>Оплата за продукцию по дог. №279/26, НДС 12%</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>126954000</v>
+        <v>147357000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46251</v>
+        <v>46266</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>1846000</v>
+        <v>9157000</v>
       </c>
       <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Afrosiyob Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>396615468</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000992552358001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ijtimoiy soliq</t>
+          <t>Оплата за товары согласно с/ф №4477</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>125108000</v>
+        <v>138200000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46251</v>
+        <v>46267</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
-      <c r="C102" s="2" t="n">
-        <v>1846000</v>
-      </c>
-      <c r="D102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n">
+        <v>30199000</v>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Yulduz Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>398152432</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000764681463001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июль 2026 г.</t>
+          <t>Mahsulot uchun to'lov, shartnoma №99/26, QQS 12%</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>123262000</v>
+        <v>168399000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46252</v>
+        <v>46268</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n">
-        <v>32309000</v>
-      </c>
+      <c r="C103" s="2" t="n">
+        <v>5363000</v>
+      </c>
+      <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Termiz Trans Servis MChJ</t>
+          <t>Ilhom Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>215614818</t>
+          <t>277606955</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000515765228001</t>
+          <t>20208000466239816001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8389 18.08.2026, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №6465</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>155571000</v>
+        <v>163036000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46252</v>
+        <v>46268</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>5687000</v>
+        <v>7358000</v>
       </c>
       <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Qarshi Mehmonxona MChJ</t>
+          <t>Afrosiyob Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>252244188</t>
+          <t>396615468</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000444491128001</t>
+          <t>20208000992552358001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №5706</t>
+          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №212/26</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>149884000</v>
+        <v>155678000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46253</v>
+        <v>46269</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
       <c r="C105" s="2" t="n"/>
       <c r="D105" s="2" t="n">
-        <v>21185000</v>
+        <v>18969000</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Chirchiq Agro Servis AJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>320468286</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000657192854001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4421,37 +4416,37 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №5974 19.08.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №889 от 04.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>171069000</v>
+        <v>174647000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46253</v>
+        <v>46272</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
       <c r="C106" s="2" t="n"/>
       <c r="D106" s="2" t="n">
-        <v>9879000</v>
+        <v>84428000</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4461,77 +4456,77 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8150 19.08.2026, QQS bilan</t>
+          <t>Оплата по с/ф №6430 за поставленный товар</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>180948000</v>
+        <v>259075000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46253</v>
+        <v>46272</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
-      <c r="C107" s="2" t="n">
-        <v>8414000</v>
-      </c>
-      <c r="D107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n">
+        <v>11819000</v>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Qarshi Mehmonxona MChJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>252244188</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000444491128001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8932</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №37/26, НДС 12%</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>172534000</v>
+        <v>270894000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46254</v>
+        <v>46272</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
       <c r="C108" s="2" t="n"/>
       <c r="D108" s="2" t="n">
-        <v>3384000</v>
+        <v>9813000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Gulshan Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>361481815</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000576522897001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4541,37 +4536,37 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1398</t>
+          <t>Оплата за продукцию по дог. №292/26, НДС 12%</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>175918000</v>
+        <v>280707000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46254</v>
+        <v>46272</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
       <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="n">
-        <v>1908000</v>
+        <v>4062000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Termiz Trans Servis MChJ</t>
+          <t>Gulshan Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>215614818</t>
+          <t>361481815</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000515765228001</t>
+          <t>20208000576522897001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4581,397 +4576,387 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Yetkazilga tovar uchun to'lov h/f №145</t>
+          <t>Оплата по с/ф №3638 за поставленный товар</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>177826000</v>
+        <v>284769000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46254</v>
+        <v>46272</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>15802000</v>
+        <v>2292000</v>
       </c>
       <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Navro'z Qurilish Materiallari MChJ</t>
+          <t>Navro'z Qurilish Materiallari AJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>240187768</t>
+          <t>313530644</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000945086482001</t>
+          <t>20208000179955104001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №31/26</t>
+          <t>Арендная плата за сентябрь 2026 г. по договору №15/25</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>162024000</v>
+        <v>282477000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46255</v>
+        <v>46272</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>3516000</v>
+        <v>14702000</v>
       </c>
       <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>QQS iyul 2026 uchun</t>
+          <t>Перечисление заработной платы за август 2026 г. согласно реестру №3792</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>158508000</v>
+        <v>267775000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46255</v>
+        <v>46273</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
-      <c r="C112" s="2" t="n">
-        <v>3580000</v>
-      </c>
-      <c r="D112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n">
+        <v>9674000</v>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Navro'z Qurilish Materiallari MChJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>240187768</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000945086482001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №51/26, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №2665 от 08.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>154928000</v>
+        <v>277449000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46255</v>
+        <v>46274</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
-      <c r="C113" s="2" t="n">
-        <v>18266000</v>
-      </c>
-      <c r="D113" s="2" t="n"/>
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" s="2" t="n">
+        <v>7864000</v>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Saodat Un Mahsulotlari XK</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>212729239</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000763758455001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №205/26, QQS BILAN</t>
+          <t>Предоплата за товар по договору №18/26 от 09.09.2026</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>136662000</v>
+        <v>285313000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46258</v>
+        <v>46274</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
       <c r="C114" s="2" t="n"/>
       <c r="D114" s="2" t="n">
-        <v>6624000</v>
+        <v>7506000</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sarbon Metall Servis MChJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>336981524</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000287646814001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8587</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №166/26, QQS 12%</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>143286000</v>
+        <v>292819000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46258</v>
+        <v>46275</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n">
-        <v>2128000</v>
-      </c>
+      <c r="C115" s="2" t="n">
+        <v>29800000</v>
+      </c>
+      <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Namangan Mato MChJ</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>271598242</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-9040)</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000367481368001</t>
+          <t>16307000243693009417</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №24/26, QQS 12%</t>
+          <t>Kredit shartnomasi L-2025-9040 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>145414000</v>
+        <v>263019000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46258</v>
+        <v>46276</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
-      <c r="C116" s="2" t="n">
-        <v>3853000</v>
-      </c>
-      <c r="D116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n">
+        <v>3702000</v>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Samarqand Qurilish Materiallari MChJ</t>
+          <t>Yulduz Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>311741835</t>
+          <t>398152432</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000721195978001</t>
+          <t>20208000764681463001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №31/26</t>
+          <t>Оплата за продукцию по договору №128/26, НДС 12%</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>141561000</v>
+        <v>266721000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46259</v>
+        <v>46276</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
-      <c r="C117" s="2" t="n"/>
-      <c r="D117" s="2" t="n">
-        <v>8848000</v>
-      </c>
+      <c r="C117" s="2" t="n">
+        <v>35718000</v>
+      </c>
+      <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Xiva Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>246828606</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000719285477001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №133/26, QQS 12%</t>
+          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГ. №278/26</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>150409000</v>
+        <v>231003000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46260</v>
+        <v>46279</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
-      <c r="C118" s="2" t="n">
-        <v>1319000</v>
-      </c>
-      <c r="D118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n">
+        <v>6466000</v>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Ziyo Mehmonxona XK</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>389832476</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000204982757001</t>
+          <t>20208000125857744001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov avgust</t>
+          <t>Оплата за продукцию по договору №260/26, НДС 12%</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>149090000</v>
+        <v>237469000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46261</v>
+        <v>46279</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>4092000</v>
+        <v>3521000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -4981,472 +4966,477 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №37/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №106/26, QQS 12%</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>153182000</v>
+        <v>240990000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46261</v>
+        <v>46279</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
-      <c r="C120" s="2" t="n"/>
-      <c r="D120" s="2" t="n">
-        <v>2146000</v>
-      </c>
+      <c r="C120" s="2" t="n">
+        <v>2005000</v>
+      </c>
+      <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Termiz Trans Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>215614818</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000515765228001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №226/26 от 27.08.2026</t>
+          <t>Уплата социального налога за август</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>155328000</v>
+        <v>238985000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46262</v>
+        <v>46279</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
-      <c r="C121" s="2" t="n"/>
-      <c r="D121" s="2" t="n">
-        <v>7864000</v>
-      </c>
+      <c r="C121" s="2" t="n">
+        <v>2005000</v>
+      </c>
+      <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Shartnoma №239/26 bo'yicha oldindan to'lov</t>
+          <t>НАЛОГ НА ДОХОДЫ ФИЗИЧЕСКИХ ЛИЦ ЗА АВГУСТ 2026 Г.</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>163192000</v>
+        <v>236980000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46262</v>
+        <v>46279</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
-      <c r="C122" s="2" t="n"/>
-      <c r="D122" s="2" t="n">
-        <v>4085000</v>
-      </c>
+      <c r="C122" s="2" t="n">
+        <v>3009000</v>
+      </c>
+      <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Afrosiyob Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>396615468</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000992552358001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №5004</t>
+          <t>Предоплата за материалы по договору №109/26</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>167277000</v>
+        <v>233971000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46265</v>
+        <v>46279</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
-      <c r="C123" s="2" t="n"/>
-      <c r="D123" s="2" t="n">
-        <v>12298000</v>
-      </c>
+      <c r="C123" s="2" t="n">
+        <v>9609000</v>
+      </c>
+      <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Jizzax Poligraf MChJ</t>
+          <t>Afrosiyob Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>248391487</t>
+          <t>396615468</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000989998587001</t>
+          <t>20208000992552358001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №1195 за поставленный товар</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №226/26</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>179575000</v>
+        <v>224362000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46265</v>
+        <v>46279</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
-      <c r="C124" s="2" t="n"/>
-      <c r="D124" s="2" t="n">
-        <v>8386000</v>
-      </c>
+      <c r="C124" s="2" t="n">
+        <v>48534000</v>
+      </c>
+      <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Jizzax Poligraf MChJ</t>
+          <t>Ilhom Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>248391487</t>
+          <t>277606955</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000989998587001</t>
+          <t>20208000466239816001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7075 от 31.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за сырье по дог. №54/26 от 14.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>187961000</v>
+        <v>175828000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46265</v>
+        <v>46280</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
       <c r="C125" s="2" t="n"/>
       <c r="D125" s="2" t="n">
-        <v>5009000</v>
+        <v>5658000</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Qog'oz MChJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>365898324</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000621258577001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Shartnoma №18/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №202/26, НДС 12%</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>192970000</v>
+        <v>181486000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46265</v>
+        <v>46280</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n">
-        <v>4322000</v>
-      </c>
+      <c r="C126" s="2" t="n">
+        <v>7968000</v>
+      </c>
+      <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Ziyo Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>314566779</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000308579769001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5380 от 31.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за транспортные услуги по дог. №141/26</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>197292000</v>
+        <v>173518000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
-      <c r="C127" s="2" t="n"/>
-      <c r="D127" s="2" t="n">
-        <v>3554000</v>
-      </c>
+      <c r="C127" s="2" t="n">
+        <v>4189000</v>
+      </c>
+      <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Afrosiyob Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>396615468</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000992552358001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №211/26, QQS 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №6201</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>200846000</v>
+        <v>169329000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46265</v>
+        <v>46282</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
-      <c r="C128" s="2" t="n"/>
-      <c r="D128" s="2" t="n">
-        <v>2753000</v>
-      </c>
+      <c r="C128" s="2" t="n">
+        <v>7244000</v>
+      </c>
+      <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Bog'ishamol Qurilish MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>292921206</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000867142616001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №195/26, QQS 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №8591</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>203599000</v>
+        <v>162085000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46265</v>
+        <v>46286</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
-      <c r="C129" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n">
+        <v>22671000</v>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Kamalak Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №1042 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>203299000</v>
+        <v>184756000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46265</v>
+        <v>46287</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
-      <c r="C130" s="2" t="n">
-        <v>79272000</v>
-      </c>
-      <c r="D130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n">
+        <v>12299000</v>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Navro'z Qurilish Materiallari MChJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>240187768</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000945086482001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1787</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №6/26 ОТ 22.09.2026</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>124027000</v>
+        <v>197055000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46266</v>
+        <v>46287</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
       <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="n">
-        <v>1812000</v>
+        <v>8043000</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5456,157 +5446,157 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №7541 01.09.2026, QQS bilan</t>
+          <t>Shartnoma №28/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>125839000</v>
+        <v>205098000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46266</v>
+        <v>46287</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n">
-        <v>936000</v>
-      </c>
+      <c r="C132" s="2" t="n">
+        <v>3858000</v>
+      </c>
+      <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1534 01.09.2026, QQS bilan</t>
+          <t>Уплата налога на добавленную стоимость за август</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>126775000</v>
+        <v>201240000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46267</v>
+        <v>46289</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n">
-        <v>120299000</v>
-      </c>
+      <c r="C133" s="2" t="n">
+        <v>5952000</v>
+      </c>
+      <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Afrosiyob Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>396615468</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000992552358001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3076</t>
+          <t>Оплата за транспортные услуги по дог. №29/26</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>247074000</v>
+        <v>195288000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46267</v>
+        <v>46289</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
-      <c r="C134" s="2" t="n"/>
-      <c r="D134" s="2" t="n">
-        <v>4549000</v>
-      </c>
+      <c r="C134" s="2" t="n">
+        <v>114711000</v>
+      </c>
+      <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Afrosiyob Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>396615468</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000992552358001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4729</t>
+          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №4961</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>251623000</v>
+        <v>80577000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46268</v>
+        <v>46290</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
       <c r="C135" s="2" t="n"/>
       <c r="D135" s="2" t="n">
-        <v>1258000</v>
+        <v>3553000</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Termiz Trans Servis MChJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>215614818</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000515765228001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5616,77 +5606,77 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4737</t>
+          <t>Предоплата за товар по договору №164/26 от 25.09.2026</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>252881000</v>
+        <v>84130000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46269</v>
+        <v>46290</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
-      <c r="C136" s="2" t="n"/>
-      <c r="D136" s="2" t="n">
-        <v>11446000</v>
-      </c>
+      <c r="C136" s="2" t="n">
+        <v>1432000</v>
+      </c>
+      <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>356268930</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>20208000083652130001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5008</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>264327000</v>
+        <v>82698000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46272</v>
+        <v>46293</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
       <c r="C137" s="2" t="n"/>
       <c r="D137" s="2" t="n">
-        <v>2518000</v>
+        <v>38685000</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Termiz Trans Servis MChJ</t>
+          <t>Gulshan Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>215614818</t>
+          <t>361481815</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000515765228001</t>
+          <t>20208000576522897001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5696,1941 +5686,111 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8181</t>
+          <t>Оплата по счет-фактуре №5744 за поставленный товар</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>266845000</v>
+        <v>121383000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46272</v>
+        <v>46294</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="n">
-        <v>2430000</v>
+        <v>9317000</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Sarbon Metall Servis MChJ</t>
+          <t>Kamalak Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>336981524</t>
+          <t>326893011</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000287646814001</t>
+          <t>20208000905518976001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5477</t>
+          <t>Оплата за продукцию по договору №231/26, НДС 12%</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>269275000</v>
+        <v>130700000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46272</v>
+        <v>46295</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
-      <c r="C139" s="2" t="n"/>
-      <c r="D139" s="2" t="n">
-        <v>1490000</v>
-      </c>
+      <c r="C139" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D139" s="2" t="n"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Samarqand Yog'och MChJ</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>356268930</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000119055189001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Shartnoma №121/26 bo'yicha oldindan to'lov</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за сентябрь</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>270765000</v>
+        <v>130400000</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B140" t="n">
-        <v>232</v>
-      </c>
-      <c r="C140" s="2" t="n"/>
-      <c r="D140" s="2" t="n">
-        <v>1327000</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Termiz Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>215614818</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>20208000515765228001</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №167 07.09.2026, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J140" s="2" t="n">
-        <v>272092000</v>
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Итого обороты:</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="n">
+        <v>878785000</v>
+      </c>
+      <c r="D140" s="4" t="n">
+        <v>888685000</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B141" t="n">
-        <v>233</v>
-      </c>
-      <c r="C141" s="2" t="n"/>
-      <c r="D141" s="2" t="n">
-        <v>1023000</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Saodat Non MChJ</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>252929212</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>20208000658671426001</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>SHARTNOMA №152/26 BO'YICHA OLDINDAN TO'LOV</t>
-        </is>
-      </c>
-      <c r="J141" s="2" t="n">
-        <v>273115000</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B142" t="n">
-        <v>234</v>
-      </c>
-      <c r="C142" s="2" t="n"/>
-      <c r="D142" s="2" t="n">
-        <v>771000</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Yulduz Avto Ehtiyot MChJ</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>339966154</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>20208000879925523001</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>SHARTNOMA №231/26 BO'YICHA OLDINDAN TO'LOV</t>
-        </is>
-      </c>
-      <c r="J142" s="2" t="n">
-        <v>273886000</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B143" t="n">
-        <v>235</v>
-      </c>
-      <c r="C143" s="2" t="n">
-        <v>2292000</v>
-      </c>
-      <c r="D143" s="2" t="n"/>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Shodlik Qurilish AJ</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>318892467</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>20208000936687065001</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>Аренда помещения за сентябрь, дог. №81/24</t>
-        </is>
-      </c>
-      <c r="J143" s="2" t="n">
-        <v>271594000</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B144" t="n">
-        <v>236</v>
-      </c>
-      <c r="C144" s="2" t="n">
-        <v>8371000</v>
-      </c>
-      <c r="D144" s="2" t="n"/>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Navro'z Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>240187768</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>20208000945086482001</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №220/26, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J144" s="2" t="n">
-        <v>263223000</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B145" t="n">
-        <v>237</v>
-      </c>
-      <c r="C145" s="2" t="n">
-        <v>14702000</v>
-      </c>
-      <c r="D145" s="2" t="n"/>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Bodomzor Bank ATB</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>Avgust oyi uchun ish haqi, reestr №8836</t>
-        </is>
-      </c>
-      <c r="J145" s="2" t="n">
-        <v>248521000</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B146" t="n">
-        <v>238</v>
-      </c>
-      <c r="C146" s="2" t="n">
-        <v>37540000</v>
-      </c>
-      <c r="D146" s="2" t="n"/>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Qarshi Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>252244188</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>20208000444491128001</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>Xom ashyo uchun to'lov, shartn. №292/26, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J146" s="2" t="n">
-        <v>210981000</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="3" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B147" t="n">
-        <v>239</v>
-      </c>
-      <c r="C147" s="2" t="n"/>
-      <c r="D147" s="2" t="n">
-        <v>1312000</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Samarqand Yog'och MChJ</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>356268930</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>20208000119055189001</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartn. №41/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J147" s="2" t="n">
-        <v>212293000</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="3" t="n">
-        <v>46274</v>
-      </c>
-      <c r="B148" t="n">
-        <v>240</v>
-      </c>
-      <c r="C148" s="2" t="n"/>
-      <c r="D148" s="2" t="n">
-        <v>2415000</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Samarqand Yog'och MChJ</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>356268930</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>20208000119055189001</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>Shartnoma №148/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-      <c r="J148" s="2" t="n">
-        <v>214708000</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="3" t="n">
-        <v>46274</v>
-      </c>
-      <c r="B149" t="n">
-        <v>241</v>
-      </c>
-      <c r="C149" s="2" t="n"/>
-      <c r="D149" s="2" t="n">
-        <v>801000</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Samarqand Yog'och MChJ</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>356268930</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>20208000119055189001</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Оплата за товар по с/ф №7182 от 09.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J149" s="2" t="n">
-        <v>215509000</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="3" t="n">
-        <v>46274</v>
-      </c>
-      <c r="B150" t="n">
-        <v>242</v>
-      </c>
-      <c r="C150" s="2" t="n">
-        <v>7437000</v>
-      </c>
-      <c r="D150" s="2" t="n"/>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Samarqand Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>311741835</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>20208000721195978001</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №93/26, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J150" s="2" t="n">
-        <v>208072000</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="3" t="n">
-        <v>46275</v>
-      </c>
-      <c r="B151" t="n">
-        <v>243</v>
-      </c>
-      <c r="C151" s="2" t="n"/>
-      <c r="D151" s="2" t="n">
-        <v>1416000</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Samarqand Yog'och MChJ</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>356268930</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>20208000119055189001</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4067 10.09.2026, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J151" s="2" t="n">
-        <v>209488000</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="3" t="n">
-        <v>46275</v>
-      </c>
-      <c r="B152" t="n">
-        <v>244</v>
-      </c>
-      <c r="C152" s="2" t="n">
-        <v>9636000</v>
-      </c>
-      <c r="D152" s="2" t="n"/>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Samarqand Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>311741835</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>20208000721195978001</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>Tovarlar uchun to'lov h/f №5410</t>
-        </is>
-      </c>
-      <c r="J152" s="2" t="n">
-        <v>199852000</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="3" t="n">
-        <v>46275</v>
-      </c>
-      <c r="B153" t="n">
-        <v>245</v>
-      </c>
-      <c r="C153" s="2" t="n">
-        <v>29800000</v>
-      </c>
-      <c r="D153" s="2" t="n"/>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-9040)</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>16307000243693009417</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Kredit shartnomasi L-2025-9040 bo'yicha navbatdagi to'lov (09.2026)</t>
-        </is>
-      </c>
-      <c r="J153" s="2" t="n">
-        <v>170052000</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="3" t="n">
-        <v>46276</v>
-      </c>
-      <c r="B154" t="n">
-        <v>246</v>
-      </c>
-      <c r="C154" s="2" t="n"/>
-      <c r="D154" s="2" t="n">
-        <v>2202000</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Samarqand Yog'och MChJ</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>356268930</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>20208000119055189001</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №6654 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J154" s="2" t="n">
-        <v>172254000</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="3" t="n">
-        <v>46276</v>
-      </c>
-      <c r="B155" t="n">
-        <v>247</v>
-      </c>
-      <c r="C155" s="2" t="n"/>
-      <c r="D155" s="2" t="n">
-        <v>2092000</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Samarqand Yog'och MChJ</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>356268930</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>20208000119055189001</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8507</t>
-        </is>
-      </c>
-      <c r="J155" s="2" t="n">
-        <v>174346000</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="3" t="n">
-        <v>46276</v>
-      </c>
-      <c r="B156" t="n">
-        <v>248</v>
-      </c>
-      <c r="C156" s="2" t="n"/>
-      <c r="D156" s="2" t="n">
-        <v>1986000</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Samarqand Yog'och MChJ</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>356268930</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>20208000119055189001</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6787 11.09.2026, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J156" s="2" t="n">
-        <v>176332000</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B157" t="n">
-        <v>249</v>
-      </c>
-      <c r="C157" s="2" t="n"/>
-      <c r="D157" s="2" t="n">
-        <v>11751000</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Samarqand Yog'och MChJ</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>356268930</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>20208000119055189001</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartn. №120/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J157" s="2" t="n">
-        <v>188083000</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B158" t="n">
-        <v>250</v>
-      </c>
-      <c r="C158" s="2" t="n"/>
-      <c r="D158" s="2" t="n">
-        <v>7667000</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Qarshi Plastik AJ</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>265213054</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>20208000371474384001</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartn. №171/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J158" s="2" t="n">
-        <v>195750000</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B159" t="n">
-        <v>251</v>
-      </c>
-      <c r="C159" s="2" t="n">
-        <v>2005000</v>
-      </c>
-      <c r="D159" s="2" t="n"/>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Уплата социального налога за август</t>
-        </is>
-      </c>
-      <c r="J159" s="2" t="n">
-        <v>193745000</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B160" t="n">
-        <v>252</v>
-      </c>
-      <c r="C160" s="2" t="n">
-        <v>2005000</v>
-      </c>
-      <c r="D160" s="2" t="n"/>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>JShDS avgust oyi uchun</t>
-        </is>
-      </c>
-      <c r="J160" s="2" t="n">
-        <v>191740000</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="3" t="n">
-        <v>46280</v>
-      </c>
-      <c r="B161" t="n">
-        <v>253</v>
-      </c>
-      <c r="C161" s="2" t="n"/>
-      <c r="D161" s="2" t="n">
-        <v>29964000</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Samarqand Yog'och MChJ</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>356268930</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>20208000119055189001</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №250/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J161" s="2" t="n">
-        <v>221704000</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="3" t="n">
-        <v>46280</v>
-      </c>
-      <c r="B162" t="n">
-        <v>254</v>
-      </c>
-      <c r="C162" s="2" t="n">
-        <v>14751000</v>
-      </c>
-      <c r="D162" s="2" t="n"/>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Samarqand Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>311741835</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>20208000721195978001</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Оплата за овары согласно счет-фактуре №390</t>
-        </is>
-      </c>
-      <c r="J162" s="2" t="n">
-        <v>206953000</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="3" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B163" t="n">
-        <v>255</v>
-      </c>
-      <c r="C163" s="2" t="n"/>
-      <c r="D163" s="2" t="n">
-        <v>3276000</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Samarqand Yog'och MChJ</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>356268930</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>20208000119055189001</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №2045 от 16.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J163" s="2" t="n">
-        <v>210229000</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="3" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B164" t="n">
-        <v>256</v>
-      </c>
-      <c r="C164" s="2" t="n"/>
-      <c r="D164" s="2" t="n">
-        <v>13995000</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Samarqand Yog'och MChJ</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>356268930</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>20208000119055189001</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №195/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J164" s="2" t="n">
-        <v>224224000</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="3" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B165" t="n">
-        <v>257</v>
-      </c>
-      <c r="C165" s="2" t="n"/>
-      <c r="D165" s="2" t="n">
-        <v>1487000</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Termiz Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>215614818</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>20208000515765228001</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №255/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J165" s="2" t="n">
-        <v>225711000</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B166" t="n">
-        <v>258</v>
-      </c>
-      <c r="C166" s="2" t="n"/>
-      <c r="D166" s="2" t="n">
-        <v>28384000</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Samarqand Yog'och MChJ</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>356268930</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>20208000119055189001</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Shartnoma №263/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-      <c r="J166" s="2" t="n">
-        <v>254095000</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B167" t="n">
-        <v>259</v>
-      </c>
-      <c r="C167" s="2" t="n"/>
-      <c r="D167" s="2" t="n">
-        <v>7592000</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Nukus Dori-Darmon MChJ</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>231776069</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>20208000544662398001</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartn. №205/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J167" s="2" t="n">
-        <v>261687000</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B168" t="n">
-        <v>260</v>
-      </c>
-      <c r="C168" s="2" t="n"/>
-      <c r="D168" s="2" t="n">
-        <v>963000</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Jizzax Poligraf MChJ</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>248391487</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>20208000989998587001</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>Shartnoma №170/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-      <c r="J168" s="2" t="n">
-        <v>262650000</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B169" t="n">
-        <v>261</v>
-      </c>
-      <c r="C169" s="2" t="n">
-        <v>3796000</v>
-      </c>
-      <c r="D169" s="2" t="n"/>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="n">
-        <v>258854000</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="3" t="n">
-        <v>46288</v>
-      </c>
-      <c r="B170" t="n">
-        <v>262</v>
-      </c>
-      <c r="C170" s="2" t="n"/>
-      <c r="D170" s="2" t="n">
-        <v>3736000</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Jizzax Poligraf MChJ</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>248391487</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>20208000989998587001</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4318 23.09.2026, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J170" s="2" t="n">
-        <v>262590000</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="3" t="n">
-        <v>46288</v>
-      </c>
-      <c r="B171" t="n">
-        <v>263</v>
-      </c>
-      <c r="C171" s="2" t="n">
-        <v>1432000</v>
-      </c>
-      <c r="D171" s="2" t="n"/>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>200933985</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>20208000204982757001</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>Elektr energiyasi uchun to'lov</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="n">
-        <v>261158000</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="3" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B172" t="n">
-        <v>264</v>
-      </c>
-      <c r="C172" s="2" t="n"/>
-      <c r="D172" s="2" t="n">
-        <v>32924000</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Namangan Mato MChJ</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>271598242</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>20208000367481368001</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>SHARTNOMA №121/26 BO'YICHA OLDINDAN TO'LOV</t>
-        </is>
-      </c>
-      <c r="J172" s="2" t="n">
-        <v>294082000</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="3" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B173" t="n">
-        <v>265</v>
-      </c>
-      <c r="C173" s="2" t="n"/>
-      <c r="D173" s="2" t="n">
-        <v>1837000</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Termiz Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>215614818</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>20208000515765228001</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №235/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="n">
-        <v>295919000</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="3" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B174" t="n">
-        <v>266</v>
-      </c>
-      <c r="C174" s="2" t="n"/>
-      <c r="D174" s="2" t="n">
-        <v>887000</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Samarqand Yog'och MChJ</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>356268930</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>20208000119055189001</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №3911 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J174" s="2" t="n">
-        <v>296806000</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="3" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B175" t="n">
-        <v>267</v>
-      </c>
-      <c r="C175" s="2" t="n"/>
-      <c r="D175" s="2" t="n">
-        <v>858000</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Termiz Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>215614818</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>20208000515765228001</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3994 24.09.2026, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="n">
-        <v>297664000</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B176" t="n">
-        <v>268</v>
-      </c>
-      <c r="C176" s="2" t="n"/>
-      <c r="D176" s="2" t="n">
-        <v>3588000</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Samarqand Yog'och MChJ</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>356268930</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>20208000119055189001</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>Shartnoma №255/2 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-      <c r="J176" s="2" t="n">
-        <v>301252000</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B177" t="n">
-        <v>269</v>
-      </c>
-      <c r="C177" s="2" t="n"/>
-      <c r="D177" s="2" t="n">
-        <v>816000</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Samarqand Yog'och MChJ</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>356268930</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>20208000119055189001</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>Shartnoma №173/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-      <c r="J177" s="2" t="n">
-        <v>302068000</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B178" t="n">
-        <v>270</v>
-      </c>
-      <c r="C178" s="2" t="n">
-        <v>7243000</v>
-      </c>
-      <c r="D178" s="2" t="n"/>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Oltin Vodiy Qog'oz MChJ</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>397204262</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>20208000211896951001</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>Оплата за товары согласно счет-фактуре №1301</t>
-        </is>
-      </c>
-      <c r="J178" s="2" t="n">
-        <v>294825000</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B179" t="n">
-        <v>271</v>
-      </c>
-      <c r="C179" s="2" t="n">
-        <v>9056000</v>
-      </c>
-      <c r="D179" s="2" t="n"/>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Samarqand Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>311741835</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>20208000721195978001</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>TOVARLAR UCHUN TO'LOV H/F №8350</t>
-        </is>
-      </c>
-      <c r="J179" s="2" t="n">
-        <v>285769000</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B180" t="n">
-        <v>272</v>
-      </c>
-      <c r="C180" s="2" t="n"/>
-      <c r="D180" s="2" t="n">
-        <v>1270000</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Termiz Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>215614818</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>20208000515765228001</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №192/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J180" s="2" t="n">
-        <v>287039000</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B181" t="n">
-        <v>273</v>
-      </c>
-      <c r="C181" s="2" t="n">
-        <v>31227000</v>
-      </c>
-      <c r="D181" s="2" t="n"/>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Navro'z Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>240187768</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>20208000945086482001</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>Оплата за транспортные услуги по договору №287/26</t>
-        </is>
-      </c>
-      <c r="J181" s="2" t="n">
-        <v>255812000</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B182" t="n">
-        <v>274</v>
-      </c>
-      <c r="C182" s="2" t="n">
-        <v>128339000</v>
-      </c>
-      <c r="D182" s="2" t="n"/>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Samarqand Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>311741835</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>20208000721195978001</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №116/26</t>
-        </is>
-      </c>
-      <c r="J182" s="2" t="n">
-        <v>127473000</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B183" t="n">
-        <v>275</v>
-      </c>
-      <c r="C183" s="2" t="n"/>
-      <c r="D183" s="2" t="n">
-        <v>1684000</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Samarqand Yog'och MChJ</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>356268930</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>20208000119055189001</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №739 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J183" s="2" t="n">
-        <v>129157000</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B184" t="n">
-        <v>276</v>
-      </c>
-      <c r="C184" s="2" t="n"/>
-      <c r="D184" s="2" t="n">
-        <v>1543000</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Samarqand Yog'och MChJ</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>356268930</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>20208000119055189001</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №117/26 от 30.09.2026</t>
-        </is>
-      </c>
-      <c r="J184" s="2" t="n">
-        <v>130700000</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B185" t="n">
-        <v>277</v>
-      </c>
-      <c r="C185" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D185" s="2" t="n"/>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Bodomzor Bank ATB</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>Bank xizmati uchun komissiya</t>
-        </is>
-      </c>
-      <c r="J185" s="2" t="n">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Исходящий остаток на 30.09.2026:</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="n">
         <v>130400000</v>
       </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Итого обороты:</t>
-        </is>
-      </c>
-      <c r="C186" s="4" t="n">
-        <v>864202000</v>
-      </c>
-      <c r="D186" s="4" t="n">
-        <v>874102000</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Исходящий остаток на 30.09.2026:</t>
-        </is>
-      </c>
-      <c r="C187" s="4" t="n">
-        <v>130400000</v>
-      </c>
-      <c r="D187" s="4" t="n"/>
+      <c r="D141" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
